--- a/backend/data/financials_by_company/0299.HK.xlsx
+++ b/backend/data/financials_by_company/0299.HK.xlsx
@@ -667,205 +667,207 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-20383691.829304</v>
+        <v>3775375.789775</v>
       </c>
       <c r="C2" t="n">
-        <v>0.013825</v>
+        <v>0.015822</v>
       </c>
       <c r="D2" t="n">
-        <v>-571369000</v>
+        <v>145168000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1474428000</v>
+        <v>238611000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1474428000</v>
+        <v>238611000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1475757000</v>
+        <v>250169000</v>
       </c>
       <c r="H2" t="n">
-        <v>2392000</v>
+        <v>34945000</v>
       </c>
       <c r="I2" t="n">
-        <v>775859000</v>
+        <v>5234073000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2045797000</v>
+        <v>383779000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2048189000</v>
+        <v>348834000</v>
       </c>
       <c r="L2" t="n">
-        <v>-272334000</v>
+        <v>-115127000</v>
       </c>
       <c r="M2" t="n">
-        <v>272421000</v>
+        <v>125036000</v>
       </c>
       <c r="N2" t="n">
-        <v>87000</v>
+        <v>9909000</v>
       </c>
       <c r="O2" t="n">
-        <v>-21712691.829304</v>
+        <v>15333375.789775</v>
       </c>
       <c r="P2" t="n">
-        <v>-1475757000</v>
+        <v>334621000</v>
       </c>
       <c r="Q2" t="n">
-        <v>797578000</v>
+        <v>5474495000</v>
       </c>
       <c r="R2" t="n">
-        <v>-2048189000</v>
+        <v>348834000</v>
       </c>
       <c r="S2" t="n">
-        <v>109202000</v>
+        <v>104366000</v>
       </c>
       <c r="T2" t="n">
-        <v>109202000</v>
+        <v>104366000</v>
       </c>
       <c r="U2" t="n">
-        <v>-13.514</v>
+        <v>3.2062</v>
       </c>
       <c r="V2" t="n">
-        <v>-13.514</v>
+        <v>3.2062</v>
       </c>
       <c r="W2" t="n">
-        <v>-1475757000</v>
+        <v>334621000</v>
       </c>
       <c r="X2" t="n">
-        <v>-1475757000</v>
+        <v>334621000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1475757000</v>
+        <v>334621000</v>
       </c>
       <c r="AA2" t="n">
-        <v>812771000</v>
+        <v>29912000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2288528000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>304709000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>84452000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-2288528000</v>
+        <v>220257000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-32082000</v>
+        <v>3541000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2320610000</v>
+        <v>223798000</v>
       </c>
       <c r="AG2" t="n">
-        <v>170922000</v>
+        <v>-28615000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1224822000</v>
+        <v>237298000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-79364000</v>
+        <v>-296058000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20503000</v>
+        <v>23005000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1283683000</v>
+        <v>35755000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-272334000</v>
+        <v>-115127000</v>
       </c>
       <c r="AM2" t="n">
-        <v>272421000</v>
+        <v>125036000</v>
       </c>
       <c r="AN2" t="n">
-        <v>87000</v>
+        <v>9909000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-411731000</v>
+        <v>29846000</v>
       </c>
       <c r="AP2" t="n">
-        <v>21719000</v>
+        <v>240422000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>43845000</v>
+        <v>240632000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7909000</v>
+        <v>99558000</v>
       </c>
       <c r="AS2" t="n">
-        <v>35936000</v>
+        <v>141074000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-390012000</v>
+        <v>270268000</v>
       </c>
       <c r="AU2" t="n">
-        <v>775859000</v>
+        <v>5234073000</v>
       </c>
       <c r="AV2" t="n">
-        <v>385847000</v>
+        <v>5504341000</v>
       </c>
       <c r="AW2" t="n">
-        <v>385847000</v>
+        <v>5504341000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-14916407.73329</v>
+        <v>-4956943.059928</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07191</v>
+        <v>0.141761</v>
       </c>
       <c r="D3" t="n">
-        <v>-544294000</v>
+        <v>-819807000</v>
       </c>
       <c r="E3" t="n">
-        <v>-207432000</v>
+        <v>-34967000</v>
       </c>
       <c r="F3" t="n">
-        <v>-207432000</v>
+        <v>-34967000</v>
       </c>
       <c r="G3" t="n">
-        <v>-601331000</v>
+        <v>-787049000</v>
       </c>
       <c r="H3" t="n">
-        <v>6423000</v>
+        <v>21107000</v>
       </c>
       <c r="I3" t="n">
-        <v>1425913000</v>
+        <v>2142594000</v>
       </c>
       <c r="J3" t="n">
-        <v>-751726000</v>
+        <v>-854774000</v>
       </c>
       <c r="K3" t="n">
-        <v>-758149000</v>
+        <v>-875881000</v>
       </c>
       <c r="L3" t="n">
-        <v>-132903000</v>
+        <v>-181819000</v>
       </c>
       <c r="M3" t="n">
-        <v>133787000</v>
+        <v>185902000</v>
       </c>
       <c r="N3" t="n">
-        <v>884000</v>
+        <v>4083000</v>
       </c>
       <c r="O3" t="n">
-        <v>-408815407.73329</v>
+        <v>-757038943.0599281</v>
       </c>
       <c r="P3" t="n">
-        <v>-601331000</v>
+        <v>-787049000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1449740000</v>
+        <v>2314157000</v>
       </c>
       <c r="R3" t="n">
-        <v>-758149000</v>
+        <v>-875881000</v>
       </c>
       <c r="S3" t="n">
         <v>109202000</v>
@@ -874,145 +876,147 @@
         <v>109202000</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.5066</v>
+        <v>-7.2073</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.5066</v>
+        <v>-7.2073</v>
       </c>
       <c r="W3" t="n">
-        <v>-601331000</v>
+        <v>-787049000</v>
       </c>
       <c r="X3" t="n">
-        <v>-601331000</v>
+        <v>-787049000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-601331000</v>
+        <v>-787049000</v>
       </c>
       <c r="AA3" t="n">
-        <v>226466000</v>
+        <v>124215000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-827797000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>-911264000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-827797000</v>
+        <v>-911264000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-64139000</v>
+        <v>-150519000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-891936000</v>
+        <v>-1061783000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-133750000</v>
+        <v>4342000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-184438000</v>
+        <v>-34967000</v>
       </c>
       <c r="AI3" t="n">
-        <v>141882000</v>
+        <v>-2214000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42556000</v>
+        <v>12673000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>24508000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-132903000</v>
+        <v>-181819000</v>
       </c>
       <c r="AM3" t="n">
-        <v>133787000</v>
+        <v>185902000</v>
       </c>
       <c r="AN3" t="n">
-        <v>884000</v>
+        <v>4083000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-246714000</v>
+        <v>-696690000</v>
       </c>
       <c r="AP3" t="n">
-        <v>23827000</v>
+        <v>171563000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>68943000</v>
+        <v>172075000</v>
       </c>
       <c r="AR3" t="n">
-        <v>14530000</v>
+        <v>53119000</v>
       </c>
       <c r="AS3" t="n">
-        <v>54413000</v>
+        <v>118956000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-222887000</v>
+        <v>-525127000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1425913000</v>
+        <v>2142594000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1203026000</v>
+        <v>1617467000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1203026000</v>
+        <v>1617467000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-4956943.059928</v>
+        <v>-14916407.73329</v>
       </c>
       <c r="C4" t="n">
-        <v>0.141761</v>
+        <v>0.07191</v>
       </c>
       <c r="D4" t="n">
-        <v>-819807000</v>
+        <v>-544294000</v>
       </c>
       <c r="E4" t="n">
-        <v>-34967000</v>
+        <v>-207432000</v>
       </c>
       <c r="F4" t="n">
-        <v>-34967000</v>
+        <v>-207432000</v>
       </c>
       <c r="G4" t="n">
-        <v>-787049000</v>
+        <v>-601331000</v>
       </c>
       <c r="H4" t="n">
-        <v>21107000</v>
+        <v>6423000</v>
       </c>
       <c r="I4" t="n">
-        <v>2142594000</v>
+        <v>1425913000</v>
       </c>
       <c r="J4" t="n">
-        <v>-854774000</v>
+        <v>-751726000</v>
       </c>
       <c r="K4" t="n">
-        <v>-875881000</v>
+        <v>-758149000</v>
       </c>
       <c r="L4" t="n">
-        <v>-181819000</v>
+        <v>-132903000</v>
       </c>
       <c r="M4" t="n">
-        <v>185902000</v>
+        <v>133787000</v>
       </c>
       <c r="N4" t="n">
-        <v>4083000</v>
+        <v>884000</v>
       </c>
       <c r="O4" t="n">
-        <v>-757038943.0599281</v>
+        <v>-408815407.73329</v>
       </c>
       <c r="P4" t="n">
-        <v>-787049000</v>
+        <v>-601331000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2314157000</v>
+        <v>1449740000</v>
       </c>
       <c r="R4" t="n">
-        <v>-875881000</v>
+        <v>-758149000</v>
       </c>
       <c r="S4" t="n">
         <v>109202000</v>
@@ -1021,240 +1025,236 @@
         <v>109202000</v>
       </c>
       <c r="U4" t="n">
-        <v>-7.2073</v>
+        <v>-5.5066</v>
       </c>
       <c r="V4" t="n">
-        <v>-7.2073</v>
+        <v>-5.5066</v>
       </c>
       <c r="W4" t="n">
-        <v>-787049000</v>
+        <v>-601331000</v>
       </c>
       <c r="X4" t="n">
-        <v>-787049000</v>
+        <v>-601331000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-787049000</v>
+        <v>-601331000</v>
       </c>
       <c r="AA4" t="n">
-        <v>124215000</v>
+        <v>226466000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-911264000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>-827797000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-911264000</v>
+        <v>-827797000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-150519000</v>
+        <v>-64139000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1061783000</v>
+        <v>-891936000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4342000</v>
+        <v>-133750000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-34967000</v>
+        <v>-184438000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2214000</v>
+        <v>141882000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12673000</v>
+        <v>42556000</v>
       </c>
       <c r="AK4" t="n">
-        <v>24508000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-181819000</v>
+        <v>-132903000</v>
       </c>
       <c r="AM4" t="n">
-        <v>185902000</v>
+        <v>133787000</v>
       </c>
       <c r="AN4" t="n">
-        <v>4083000</v>
+        <v>884000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-696690000</v>
+        <v>-246714000</v>
       </c>
       <c r="AP4" t="n">
-        <v>171563000</v>
+        <v>23827000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>172075000</v>
+        <v>68943000</v>
       </c>
       <c r="AR4" t="n">
-        <v>53119000</v>
+        <v>14530000</v>
       </c>
       <c r="AS4" t="n">
-        <v>118956000</v>
+        <v>54413000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-525127000</v>
+        <v>-222887000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2142594000</v>
+        <v>1425913000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1617467000</v>
+        <v>1203026000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1617467000</v>
+        <v>1203026000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>3775375.789775</v>
+        <v>-20383691.829304</v>
       </c>
       <c r="C5" t="n">
-        <v>0.015822</v>
+        <v>0.013825</v>
       </c>
       <c r="D5" t="n">
-        <v>145168000</v>
+        <v>-571369000</v>
       </c>
       <c r="E5" t="n">
-        <v>238611000</v>
+        <v>-1474428000</v>
       </c>
       <c r="F5" t="n">
-        <v>238611000</v>
+        <v>-1474428000</v>
       </c>
       <c r="G5" t="n">
-        <v>250169000</v>
+        <v>-1475757000</v>
       </c>
       <c r="H5" t="n">
-        <v>34945000</v>
+        <v>2392000</v>
       </c>
       <c r="I5" t="n">
-        <v>5234073000</v>
+        <v>775859000</v>
       </c>
       <c r="J5" t="n">
-        <v>383779000</v>
+        <v>-2045797000</v>
       </c>
       <c r="K5" t="n">
-        <v>348834000</v>
+        <v>-2048189000</v>
       </c>
       <c r="L5" t="n">
-        <v>-115127000</v>
+        <v>-272334000</v>
       </c>
       <c r="M5" t="n">
-        <v>125036000</v>
+        <v>272421000</v>
       </c>
       <c r="N5" t="n">
-        <v>9909000</v>
+        <v>87000</v>
       </c>
       <c r="O5" t="n">
-        <v>15333375.789775</v>
+        <v>-21712691.829304</v>
       </c>
       <c r="P5" t="n">
-        <v>334621000</v>
+        <v>-1475757000</v>
       </c>
       <c r="Q5" t="n">
-        <v>5474495000</v>
+        <v>797578000</v>
       </c>
       <c r="R5" t="n">
-        <v>348834000</v>
+        <v>-2048189000</v>
       </c>
       <c r="S5" t="n">
-        <v>104366000</v>
+        <v>109202000</v>
       </c>
       <c r="T5" t="n">
-        <v>104366000</v>
+        <v>109202000</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2062</v>
+        <v>-13.514</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2062</v>
+        <v>-13.514</v>
       </c>
       <c r="W5" t="n">
-        <v>334621000</v>
+        <v>-1475757000</v>
       </c>
       <c r="X5" t="n">
-        <v>334621000</v>
+        <v>-1475757000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>334621000</v>
+        <v>-1475757000</v>
       </c>
       <c r="AA5" t="n">
-        <v>29912000</v>
+        <v>812771000</v>
       </c>
       <c r="AB5" t="n">
-        <v>304709000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>84452000</v>
-      </c>
+        <v>-2288528000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>220257000</v>
+        <v>-2288528000</v>
       </c>
       <c r="AE5" t="n">
-        <v>3541000</v>
+        <v>-32082000</v>
       </c>
       <c r="AF5" t="n">
-        <v>223798000</v>
+        <v>-2320610000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-28615000</v>
+        <v>170922000</v>
       </c>
       <c r="AH5" t="n">
-        <v>237298000</v>
+        <v>-1224822000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-296058000</v>
+        <v>-79364000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23005000</v>
+        <v>20503000</v>
       </c>
       <c r="AK5" t="n">
-        <v>35755000</v>
+        <v>1283683000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-115127000</v>
+        <v>-272334000</v>
       </c>
       <c r="AM5" t="n">
-        <v>125036000</v>
+        <v>272421000</v>
       </c>
       <c r="AN5" t="n">
-        <v>9909000</v>
+        <v>87000</v>
       </c>
       <c r="AO5" t="n">
-        <v>29846000</v>
+        <v>-411731000</v>
       </c>
       <c r="AP5" t="n">
-        <v>240422000</v>
+        <v>21719000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>240632000</v>
+        <v>43845000</v>
       </c>
       <c r="AR5" t="n">
-        <v>99558000</v>
+        <v>7909000</v>
       </c>
       <c r="AS5" t="n">
-        <v>141074000</v>
+        <v>35936000</v>
       </c>
       <c r="AT5" t="n">
-        <v>270268000</v>
+        <v>-390012000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5234073000</v>
+        <v>775859000</v>
       </c>
       <c r="AV5" t="n">
-        <v>5504341000</v>
+        <v>385847000</v>
       </c>
       <c r="AW5" t="n">
-        <v>5504341000</v>
+        <v>385847000</v>
       </c>
     </row>
   </sheetData>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>109202495</v>
@@ -1614,189 +1614,197 @@
         <v>109202495</v>
       </c>
       <c r="D2" t="n">
-        <v>3662517000</v>
+        <v>7726081000</v>
       </c>
       <c r="E2" t="n">
-        <v>3677351000</v>
+        <v>8132018000</v>
       </c>
       <c r="F2" t="n">
-        <v>-305147000</v>
+        <v>2953934000</v>
       </c>
       <c r="G2" t="n">
-        <v>3360636000</v>
+        <v>11021408000</v>
       </c>
       <c r="H2" t="n">
-        <v>-530926000</v>
+        <v>4042107000</v>
       </c>
       <c r="I2" t="n">
-        <v>-305147000</v>
+        <v>2953934000</v>
       </c>
       <c r="J2" t="n">
-        <v>11568000</v>
+        <v>64544000</v>
       </c>
       <c r="K2" t="n">
-        <v>-305147000</v>
+        <v>2953934000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1668000</v>
+        <v>5617320000</v>
       </c>
       <c r="M2" t="n">
-        <v>-95764000</v>
+        <v>4791957000</v>
       </c>
       <c r="N2" t="n">
-        <v>209383000</v>
+        <v>1838023000</v>
       </c>
       <c r="O2" t="n">
-        <v>-305147000</v>
+        <v>2953934000</v>
       </c>
       <c r="P2" t="n">
         <v>4149000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4443433000</v>
+        <v>-1849337000</v>
       </c>
       <c r="R2" t="n">
         <v>3419127000</v>
       </c>
       <c r="S2" t="n">
-        <v>5460000</v>
+        <v>273006000</v>
       </c>
       <c r="T2" t="n">
-        <v>5460000</v>
+        <v>273006000</v>
       </c>
       <c r="U2" t="n">
-        <v>7342605000</v>
+        <v>15358362000</v>
       </c>
       <c r="V2" t="n">
-        <v>317074000</v>
+        <v>3455162000</v>
       </c>
       <c r="W2" t="n">
-        <v>2324000</v>
+        <v>643522000</v>
       </c>
       <c r="X2" t="n">
-        <v>314750000</v>
+        <v>2722012000</v>
       </c>
       <c r="Y2" t="n">
-        <v>11271000</v>
+        <v>58626000</v>
       </c>
       <c r="Z2" t="n">
-        <v>303479000</v>
+        <v>2663386000</v>
       </c>
       <c r="AA2" t="n">
-        <v>7025531000</v>
+        <v>11903200000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3362601000</v>
+        <v>5410006000</v>
       </c>
       <c r="AC2" t="n">
-        <v>297000</v>
+        <v>5918000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3362304000</v>
+        <v>5404088000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2673196000</v>
+        <v>3782049000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1111212000</v>
+        <v>665947000</v>
       </c>
       <c r="AG2" t="n">
-        <v>136503000</v>
+        <v>175751000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1425481000</v>
+        <v>2940351000</v>
       </c>
       <c r="AI2" t="n">
-        <v>7246841000</v>
+        <v>20150319000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>752236000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>4205012000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>202000</v>
+        <v>4694000</v>
       </c>
       <c r="AM2" t="n">
-        <v>202000</v>
+        <v>4694000</v>
       </c>
       <c r="AN2" t="n">
-        <v>736216000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>4063202000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>15818000</v>
+        <v>137116000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-9759000</v>
+        <v>-132453000</v>
       </c>
       <c r="AS2" t="n">
-        <v>25577000</v>
+        <v>269569000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4969000</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>1756000</v>
+        <v>9316000</v>
       </c>
       <c r="AW2" t="n">
-        <v>9498000</v>
+        <v>74071000</v>
       </c>
       <c r="AX2" t="n">
-        <v>9354000</v>
+        <v>186182000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6494605000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>15945307000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="n">
-        <v>24275000</v>
+        <v>381882000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1661904000</v>
+        <v>4267383000</v>
       </c>
       <c r="BD2" t="n">
-        <v>4109554000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>10016940000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>452000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>4109554000</v>
+        <v>10016488000</v>
       </c>
       <c r="BG2" t="n">
-        <v>534826000</v>
+        <v>683245000</v>
       </c>
       <c r="BH2" t="n">
-        <v>49661000</v>
+        <v>177982000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1571000</v>
+        <v>76482000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-8242000</v>
+        <v>-697000</v>
       </c>
       <c r="BK2" t="n">
-        <v>9813000</v>
+        <v>77179000</v>
       </c>
       <c r="BL2" t="n">
-        <v>112814000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>109548000</v>
-      </c>
+        <v>341393000</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>3266000</v>
+        <v>341393000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3266000</v>
+        <v>341393000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>109202495</v>
@@ -1805,46 +1813,46 @@
         <v>109202495</v>
       </c>
       <c r="D3" t="n">
-        <v>4646412000</v>
+        <v>6392697000</v>
       </c>
       <c r="E3" t="n">
-        <v>4695926000</v>
+        <v>6533755000</v>
       </c>
       <c r="F3" t="n">
-        <v>1189207000</v>
+        <v>1675868000</v>
       </c>
       <c r="G3" t="n">
-        <v>5859462000</v>
+        <v>8156980000</v>
       </c>
       <c r="H3" t="n">
-        <v>1593427000</v>
+        <v>946027000</v>
       </c>
       <c r="I3" t="n">
-        <v>1189207000</v>
+        <v>1675868000</v>
       </c>
       <c r="J3" t="n">
-        <v>25671000</v>
+        <v>52643000</v>
       </c>
       <c r="K3" t="n">
-        <v>1189207000</v>
+        <v>1675868000</v>
       </c>
       <c r="L3" t="n">
-        <v>1906292000</v>
+        <v>2589403000</v>
       </c>
       <c r="M3" t="n">
-        <v>2225585000</v>
+        <v>3192554000</v>
       </c>
       <c r="N3" t="n">
-        <v>1036378000</v>
+        <v>1516686000</v>
       </c>
       <c r="O3" t="n">
-        <v>1189207000</v>
+        <v>1675868000</v>
       </c>
       <c r="P3" t="n">
         <v>4149000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2967676000</v>
+        <v>-2370405000</v>
       </c>
       <c r="R3" t="n">
         <v>3419127000</v>
@@ -1856,140 +1864,144 @@
         <v>5460000</v>
       </c>
       <c r="U3" t="n">
-        <v>8922013000</v>
+        <v>13491983000</v>
       </c>
       <c r="V3" t="n">
-        <v>783528000</v>
+        <v>1331626000</v>
       </c>
       <c r="W3" t="n">
-        <v>42173000</v>
+        <v>371029000</v>
       </c>
       <c r="X3" t="n">
-        <v>741355000</v>
+        <v>960597000</v>
       </c>
       <c r="Y3" t="n">
-        <v>24270000</v>
+        <v>47062000</v>
       </c>
       <c r="Z3" t="n">
-        <v>717085000</v>
+        <v>913535000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8138485000</v>
+        <v>12160357000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3954571000</v>
+        <v>5573158000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1401000</v>
+        <v>5581000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3953170000</v>
+        <v>5567577000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3053052000</v>
+        <v>3809910000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1482279000</v>
+        <v>1088605000</v>
       </c>
       <c r="AG3" t="n">
-        <v>163047000</v>
+        <v>191511000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1407726000</v>
+        <v>2529794000</v>
       </c>
       <c r="AI3" t="n">
-        <v>11147598000</v>
+        <v>16684537000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1415686000</v>
+        <v>3578153000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>354000</v>
+        <v>1253000</v>
       </c>
       <c r="AM3" t="n">
-        <v>354000</v>
+        <v>1253000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1358260000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+        <v>3492852000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>57072000</v>
+        <v>84048000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-148274000</v>
+        <v>-163190000</v>
       </c>
       <c r="AS3" t="n">
-        <v>205346000</v>
+        <v>247238000</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>84048000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>7817000</v>
+        <v>9548000</v>
       </c>
       <c r="AW3" t="n">
-        <v>45454000</v>
+        <v>72132000</v>
       </c>
       <c r="AX3" t="n">
-        <v>152075000</v>
+        <v>165558000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9731912000</v>
+        <v>13106384000</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>52081000</v>
+        <v>441325000</v>
       </c>
       <c r="BC3" t="n">
-        <v>2953885000</v>
+        <v>3889121000</v>
       </c>
       <c r="BD3" t="n">
-        <v>4722974000</v>
+        <v>8086954000</v>
       </c>
       <c r="BE3" t="n">
-        <v>387000</v>
+        <v>453000</v>
       </c>
       <c r="BF3" t="n">
-        <v>4722587000</v>
+        <v>8086501000</v>
       </c>
       <c r="BG3" t="n">
-        <v>454931000</v>
+        <v>494294000</v>
       </c>
       <c r="BH3" t="n">
-        <v>75497000</v>
+        <v>84474000</v>
       </c>
       <c r="BI3" t="n">
-        <v>12009000</v>
+        <v>21801000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-888000</v>
+        <v>-17031000</v>
       </c>
       <c r="BK3" t="n">
-        <v>12897000</v>
+        <v>38832000</v>
       </c>
       <c r="BL3" t="n">
-        <v>1460535000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1436692000</v>
-      </c>
+        <v>88415000</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>23843000</v>
+        <v>88415000</v>
       </c>
       <c r="BO3" t="n">
-        <v>23843000</v>
+        <v>88415000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>109202495</v>
@@ -1998,46 +2010,46 @@
         <v>109202495</v>
       </c>
       <c r="D4" t="n">
-        <v>6392697000</v>
+        <v>4646412000</v>
       </c>
       <c r="E4" t="n">
-        <v>6533755000</v>
+        <v>4695926000</v>
       </c>
       <c r="F4" t="n">
-        <v>1675868000</v>
+        <v>1189207000</v>
       </c>
       <c r="G4" t="n">
-        <v>8156980000</v>
+        <v>5859462000</v>
       </c>
       <c r="H4" t="n">
-        <v>946027000</v>
+        <v>1593427000</v>
       </c>
       <c r="I4" t="n">
-        <v>1675868000</v>
+        <v>1189207000</v>
       </c>
       <c r="J4" t="n">
-        <v>52643000</v>
+        <v>25671000</v>
       </c>
       <c r="K4" t="n">
-        <v>1675868000</v>
+        <v>1189207000</v>
       </c>
       <c r="L4" t="n">
-        <v>2589403000</v>
+        <v>1906292000</v>
       </c>
       <c r="M4" t="n">
-        <v>3192554000</v>
+        <v>2225585000</v>
       </c>
       <c r="N4" t="n">
-        <v>1516686000</v>
+        <v>1036378000</v>
       </c>
       <c r="O4" t="n">
-        <v>1675868000</v>
+        <v>1189207000</v>
       </c>
       <c r="P4" t="n">
         <v>4149000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2370405000</v>
+        <v>-2967676000</v>
       </c>
       <c r="R4" t="n">
         <v>3419127000</v>
@@ -2049,144 +2061,140 @@
         <v>5460000</v>
       </c>
       <c r="U4" t="n">
-        <v>13491983000</v>
+        <v>8922013000</v>
       </c>
       <c r="V4" t="n">
-        <v>1331626000</v>
+        <v>783528000</v>
       </c>
       <c r="W4" t="n">
-        <v>371029000</v>
+        <v>42173000</v>
       </c>
       <c r="X4" t="n">
-        <v>960597000</v>
+        <v>741355000</v>
       </c>
       <c r="Y4" t="n">
-        <v>47062000</v>
+        <v>24270000</v>
       </c>
       <c r="Z4" t="n">
-        <v>913535000</v>
+        <v>717085000</v>
       </c>
       <c r="AA4" t="n">
-        <v>12160357000</v>
+        <v>8138485000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5573158000</v>
+        <v>3954571000</v>
       </c>
       <c r="AC4" t="n">
-        <v>5581000</v>
+        <v>1401000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5567577000</v>
+        <v>3953170000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3809910000</v>
+        <v>3053052000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1088605000</v>
+        <v>1482279000</v>
       </c>
       <c r="AG4" t="n">
-        <v>191511000</v>
+        <v>163047000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2529794000</v>
+        <v>1407726000</v>
       </c>
       <c r="AI4" t="n">
-        <v>16684537000</v>
+        <v>11147598000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3578153000</v>
+        <v>1415686000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>1253000</v>
+        <v>354000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1253000</v>
+        <v>354000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3492852000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>1358260000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>84048000</v>
+        <v>57072000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-163190000</v>
+        <v>-148274000</v>
       </c>
       <c r="AS4" t="n">
-        <v>247238000</v>
+        <v>205346000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="n">
-        <v>84048000</v>
-      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>9548000</v>
+        <v>7817000</v>
       </c>
       <c r="AW4" t="n">
-        <v>72132000</v>
+        <v>45454000</v>
       </c>
       <c r="AX4" t="n">
-        <v>165558000</v>
+        <v>152075000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13106384000</v>
+        <v>9731912000</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>441325000</v>
+        <v>52081000</v>
       </c>
       <c r="BC4" t="n">
-        <v>3889121000</v>
+        <v>2953885000</v>
       </c>
       <c r="BD4" t="n">
-        <v>8086954000</v>
+        <v>4722974000</v>
       </c>
       <c r="BE4" t="n">
-        <v>453000</v>
+        <v>387000</v>
       </c>
       <c r="BF4" t="n">
-        <v>8086501000</v>
+        <v>4722587000</v>
       </c>
       <c r="BG4" t="n">
-        <v>494294000</v>
+        <v>454931000</v>
       </c>
       <c r="BH4" t="n">
-        <v>84474000</v>
+        <v>75497000</v>
       </c>
       <c r="BI4" t="n">
-        <v>21801000</v>
+        <v>12009000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-17031000</v>
+        <v>-888000</v>
       </c>
       <c r="BK4" t="n">
-        <v>38832000</v>
+        <v>12897000</v>
       </c>
       <c r="BL4" t="n">
-        <v>88415000</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
+        <v>1460535000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1436692000</v>
+      </c>
       <c r="BN4" t="n">
-        <v>88415000</v>
+        <v>23843000</v>
       </c>
       <c r="BO4" t="n">
-        <v>88415000</v>
+        <v>23843000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>109202495</v>
@@ -2195,192 +2203,184 @@
         <v>109202495</v>
       </c>
       <c r="D5" t="n">
-        <v>7726081000</v>
+        <v>3662517000</v>
       </c>
       <c r="E5" t="n">
-        <v>8132018000</v>
+        <v>3677351000</v>
       </c>
       <c r="F5" t="n">
-        <v>2953934000</v>
+        <v>-305147000</v>
       </c>
       <c r="G5" t="n">
-        <v>11021408000</v>
+        <v>3360636000</v>
       </c>
       <c r="H5" t="n">
-        <v>4042107000</v>
+        <v>-530926000</v>
       </c>
       <c r="I5" t="n">
-        <v>2953934000</v>
+        <v>-305147000</v>
       </c>
       <c r="J5" t="n">
-        <v>64544000</v>
+        <v>11568000</v>
       </c>
       <c r="K5" t="n">
-        <v>2953934000</v>
+        <v>-305147000</v>
       </c>
       <c r="L5" t="n">
-        <v>5617320000</v>
+        <v>-1668000</v>
       </c>
       <c r="M5" t="n">
-        <v>4791957000</v>
+        <v>-95764000</v>
       </c>
       <c r="N5" t="n">
-        <v>1838023000</v>
+        <v>209383000</v>
       </c>
       <c r="O5" t="n">
-        <v>2953934000</v>
+        <v>-305147000</v>
       </c>
       <c r="P5" t="n">
         <v>4149000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1849337000</v>
+        <v>-4443433000</v>
       </c>
       <c r="R5" t="n">
         <v>3419127000</v>
       </c>
       <c r="S5" t="n">
-        <v>273006000</v>
+        <v>5460000</v>
       </c>
       <c r="T5" t="n">
-        <v>273006000</v>
+        <v>5460000</v>
       </c>
       <c r="U5" t="n">
-        <v>15358362000</v>
+        <v>7342605000</v>
       </c>
       <c r="V5" t="n">
-        <v>3455162000</v>
+        <v>317074000</v>
       </c>
       <c r="W5" t="n">
-        <v>643522000</v>
+        <v>2324000</v>
       </c>
       <c r="X5" t="n">
-        <v>2722012000</v>
+        <v>314750000</v>
       </c>
       <c r="Y5" t="n">
-        <v>58626000</v>
+        <v>11271000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2663386000</v>
+        <v>303479000</v>
       </c>
       <c r="AA5" t="n">
-        <v>11903200000</v>
+        <v>7025531000</v>
       </c>
       <c r="AB5" t="n">
-        <v>5410006000</v>
+        <v>3362601000</v>
       </c>
       <c r="AC5" t="n">
-        <v>5918000</v>
+        <v>297000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5404088000</v>
+        <v>3362304000</v>
       </c>
       <c r="AE5" t="n">
-        <v>3782049000</v>
+        <v>2673196000</v>
       </c>
       <c r="AF5" t="n">
-        <v>665947000</v>
+        <v>1111212000</v>
       </c>
       <c r="AG5" t="n">
-        <v>175751000</v>
+        <v>136503000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2940351000</v>
+        <v>1425481000</v>
       </c>
       <c r="AI5" t="n">
-        <v>20150319000</v>
+        <v>7246841000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4205012000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>752236000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>4694000</v>
+        <v>202000</v>
       </c>
       <c r="AM5" t="n">
-        <v>4694000</v>
+        <v>202000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4063202000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
+        <v>736216000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>137116000</v>
+        <v>15818000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-132453000</v>
+        <v>-9759000</v>
       </c>
       <c r="AS5" t="n">
-        <v>269569000</v>
+        <v>25577000</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4969000</v>
       </c>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>9316000</v>
+        <v>1756000</v>
       </c>
       <c r="AW5" t="n">
-        <v>74071000</v>
+        <v>9498000</v>
       </c>
       <c r="AX5" t="n">
-        <v>186182000</v>
+        <v>9354000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15945307000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
+        <v>6494605000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>381882000</v>
+        <v>24275000</v>
       </c>
       <c r="BC5" t="n">
-        <v>4267383000</v>
+        <v>1661904000</v>
       </c>
       <c r="BD5" t="n">
-        <v>10016940000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>452000</v>
-      </c>
+        <v>4109554000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>10016488000</v>
+        <v>4109554000</v>
       </c>
       <c r="BG5" t="n">
-        <v>683245000</v>
+        <v>534826000</v>
       </c>
       <c r="BH5" t="n">
-        <v>177982000</v>
+        <v>49661000</v>
       </c>
       <c r="BI5" t="n">
-        <v>76482000</v>
+        <v>1571000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-697000</v>
+        <v>-8242000</v>
       </c>
       <c r="BK5" t="n">
-        <v>77179000</v>
+        <v>9813000</v>
       </c>
       <c r="BL5" t="n">
-        <v>341393000</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
+        <v>112814000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>109548000</v>
+      </c>
       <c r="BN5" t="n">
-        <v>341393000</v>
+        <v>3266000</v>
       </c>
       <c r="BO5" t="n">
-        <v>341393000</v>
+        <v>3266000</v>
       </c>
     </row>
   </sheetData>
@@ -2661,596 +2661,596 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>218416000</v>
+        <v>1707570000</v>
       </c>
       <c r="C2" t="n">
-        <v>-849051000</v>
+        <v>-7247804000</v>
       </c>
       <c r="D2" t="n">
-        <v>650530000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>5297219000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>272535000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-5398000</v>
+        <v>-34770000</v>
       </c>
       <c r="G2" t="n">
-        <v>3266000</v>
+        <v>341393000</v>
       </c>
       <c r="H2" t="n">
-        <v>23843000</v>
+        <v>735501000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2758000</v>
+        <v>-49235000</v>
       </c>
       <c r="J2" t="n">
-        <v>-17819000</v>
+        <v>-344873000</v>
       </c>
       <c r="K2" t="n">
-        <v>-261654000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>-2600495000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-110766000</v>
+      </c>
       <c r="M2" t="n">
-        <v>-62330000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-805274000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>272535000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>272535000</v>
+      </c>
       <c r="P2" t="n">
-        <v>-198521000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>-1950585000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>180000000</v>
+      </c>
       <c r="S2" t="n">
-        <v>-198521000</v>
+        <v>-2130585000</v>
       </c>
       <c r="T2" t="n">
-        <v>-849051000</v>
+        <v>-7247804000</v>
       </c>
       <c r="U2" t="n">
-        <v>650530000</v>
+        <v>5117219000</v>
       </c>
       <c r="V2" t="n">
-        <v>20021000</v>
+        <v>513282000</v>
       </c>
       <c r="W2" t="n">
-        <v>25669000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>188429000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-328000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>182045000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>415604000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-328000</v>
+        <v>-233559000</v>
       </c>
       <c r="AD2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+        <v>178023000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-548000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-128000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-128000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-5345000</v>
+        <v>-34539000</v>
       </c>
       <c r="AI2" t="n">
-        <v>53000</v>
+        <v>103000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-5398000</v>
+        <v>-34642000</v>
       </c>
       <c r="AK2" t="n">
-        <v>223814000</v>
+        <v>1742340000</v>
       </c>
       <c r="AL2" t="n">
-        <v>780000</v>
+        <v>-159735000</v>
       </c>
       <c r="AM2" t="n">
-        <v>87000</v>
+        <v>9924000</v>
       </c>
       <c r="AN2" t="n">
-        <v>246341000</v>
+        <v>1622412000</v>
       </c>
       <c r="AO2" t="n">
-        <v>94483000</v>
+        <v>2137536000</v>
       </c>
       <c r="AP2" t="n">
-        <v>356053000</v>
+        <v>1153491000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23681000</v>
+        <v>-1453808000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-227876000</v>
+        <v>-214807000</v>
       </c>
       <c r="AS2" t="n">
-        <v>247397000</v>
+        <v>130717000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2392000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>34945000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4303000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>2392000</v>
+        <v>30642000</v>
       </c>
       <c r="AW2" t="n">
-        <v>421960000</v>
+        <v>-38669000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1976000</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>-29000</v>
+        <v>1000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-56004000</v>
+        <v>-399199000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-2320610000</v>
+        <v>308250000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>89874000</v>
+        <v>949196000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1433302000</v>
+        <v>-3752834000</v>
       </c>
       <c r="D3" t="n">
-        <v>1284360000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>2813120000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-451000</v>
+        <v>-8190000</v>
       </c>
       <c r="G3" t="n">
-        <v>23843000</v>
+        <v>88415000</v>
       </c>
       <c r="H3" t="n">
-        <v>88415000</v>
+        <v>341393000</v>
       </c>
       <c r="I3" t="n">
-        <v>9976000</v>
+        <v>-33933000</v>
       </c>
       <c r="J3" t="n">
-        <v>-74548000</v>
+        <v>-219045000</v>
       </c>
       <c r="K3" t="n">
-        <v>-267125000</v>
+        <v>-1198508000</v>
       </c>
       <c r="L3" t="n">
-        <v>-35000</v>
+        <v>1228000</v>
       </c>
       <c r="M3" t="n">
-        <v>-117028000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-259108000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>-148942000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+        <v>-939714000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="n">
-        <v>-148942000</v>
+        <v>-939714000</v>
       </c>
       <c r="T3" t="n">
-        <v>-1433302000</v>
+        <v>-3752834000</v>
       </c>
       <c r="U3" t="n">
-        <v>1284360000</v>
+        <v>2813120000</v>
       </c>
       <c r="V3" t="n">
-        <v>102252000</v>
+        <v>22077000</v>
       </c>
       <c r="W3" t="n">
-        <v>128188000</v>
+        <v>-104673000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>3946000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3946000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-38221000</v>
+        <v>-1061000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>24608000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-38221000</v>
+        <v>-25669000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12735000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+        <v>132000000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-450000</v>
+        <v>-8135000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>55000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-451000</v>
+        <v>-8190000</v>
       </c>
       <c r="AK3" t="n">
-        <v>90325000</v>
+        <v>957386000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-35307000</v>
+        <v>-67766000</v>
       </c>
       <c r="AM3" t="n">
-        <v>884000</v>
+        <v>4083000</v>
       </c>
       <c r="AN3" t="n">
-        <v>105326000</v>
+        <v>992803000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-450572000</v>
+        <v>292308000</v>
       </c>
       <c r="AP3" t="n">
-        <v>228806000</v>
+        <v>44304000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>170079000</v>
+        <v>605301000</v>
       </c>
       <c r="AR3" t="n">
-        <v>157013000</v>
+        <v>50890000</v>
       </c>
       <c r="AS3" t="n">
-        <v>116100000</v>
+        <v>179573000</v>
       </c>
       <c r="AT3" t="n">
-        <v>6423000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>21107000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
       <c r="AV3" t="n">
-        <v>6423000</v>
+        <v>21107000</v>
       </c>
       <c r="AW3" t="n">
-        <v>311272000</v>
+        <v>222953000</v>
       </c>
       <c r="AX3" t="n">
-        <v>18685000</v>
+        <v>-70865000</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>156169000</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-891936000</v>
+        <v>-1061783000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>949196000</v>
+        <v>89874000</v>
       </c>
       <c r="C4" t="n">
-        <v>-3752834000</v>
+        <v>-1433302000</v>
       </c>
       <c r="D4" t="n">
-        <v>2813120000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>1284360000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-8190000</v>
+        <v>-451000</v>
       </c>
       <c r="G4" t="n">
+        <v>23843000</v>
+      </c>
+      <c r="H4" t="n">
         <v>88415000</v>
       </c>
-      <c r="H4" t="n">
-        <v>341393000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-33933000</v>
+        <v>9976000</v>
       </c>
       <c r="J4" t="n">
-        <v>-219045000</v>
+        <v>-74548000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1198508000</v>
+        <v>-267125000</v>
       </c>
       <c r="L4" t="n">
-        <v>1228000</v>
+        <v>-35000</v>
       </c>
       <c r="M4" t="n">
-        <v>-259108000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-117028000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-939714000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
+        <v>-148942000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-939714000</v>
+        <v>-148942000</v>
       </c>
       <c r="T4" t="n">
-        <v>-3752834000</v>
+        <v>-1433302000</v>
       </c>
       <c r="U4" t="n">
-        <v>2813120000</v>
+        <v>1284360000</v>
       </c>
       <c r="V4" t="n">
-        <v>22077000</v>
+        <v>102252000</v>
       </c>
       <c r="W4" t="n">
-        <v>-104673000</v>
+        <v>128188000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>3946000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3946000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1061000</v>
+        <v>-38221000</v>
       </c>
       <c r="AB4" t="n">
-        <v>24608000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-25669000</v>
+        <v>-38221000</v>
       </c>
       <c r="AD4" t="n">
-        <v>132000000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>12735000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-8135000</v>
+        <v>-450000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55000</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-8190000</v>
+        <v>-451000</v>
       </c>
       <c r="AK4" t="n">
-        <v>957386000</v>
+        <v>90325000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-67766000</v>
+        <v>-35307000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4083000</v>
+        <v>884000</v>
       </c>
       <c r="AN4" t="n">
-        <v>992803000</v>
+        <v>105326000</v>
       </c>
       <c r="AO4" t="n">
-        <v>292308000</v>
+        <v>-450572000</v>
       </c>
       <c r="AP4" t="n">
-        <v>44304000</v>
+        <v>228806000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>605301000</v>
+        <v>170079000</v>
       </c>
       <c r="AR4" t="n">
-        <v>50890000</v>
+        <v>157013000</v>
       </c>
       <c r="AS4" t="n">
-        <v>179573000</v>
+        <v>116100000</v>
       </c>
       <c r="AT4" t="n">
-        <v>21107000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>6423000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>21107000</v>
+        <v>6423000</v>
       </c>
       <c r="AW4" t="n">
-        <v>222953000</v>
+        <v>311272000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-70865000</v>
+        <v>18685000</v>
       </c>
       <c r="AY4" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>156169000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1061783000</v>
+        <v>-891936000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1707570000</v>
+        <v>218416000</v>
       </c>
       <c r="C5" t="n">
-        <v>-7247804000</v>
+        <v>-849051000</v>
       </c>
       <c r="D5" t="n">
-        <v>5297219000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>272535000</v>
-      </c>
+        <v>650530000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-34770000</v>
+        <v>-5398000</v>
       </c>
       <c r="G5" t="n">
-        <v>341393000</v>
+        <v>3266000</v>
       </c>
       <c r="H5" t="n">
-        <v>735501000</v>
+        <v>23843000</v>
       </c>
       <c r="I5" t="n">
-        <v>-49235000</v>
+        <v>-2758000</v>
       </c>
       <c r="J5" t="n">
-        <v>-344873000</v>
+        <v>-17819000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2600495000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-110766000</v>
-      </c>
+        <v>-261654000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-805274000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>272535000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>272535000</v>
-      </c>
+        <v>-62330000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-1950585000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>180000000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>180000000</v>
-      </c>
+        <v>-198521000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-2130585000</v>
+        <v>-198521000</v>
       </c>
       <c r="T5" t="n">
-        <v>-7247804000</v>
+        <v>-849051000</v>
       </c>
       <c r="U5" t="n">
-        <v>5117219000</v>
+        <v>650530000</v>
       </c>
       <c r="V5" t="n">
-        <v>513282000</v>
+        <v>20021000</v>
       </c>
       <c r="W5" t="n">
-        <v>188429000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>25669000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>182045000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>415604000</v>
-      </c>
+        <v>-328000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-233559000</v>
+        <v>-328000</v>
       </c>
       <c r="AD5" t="n">
-        <v>178023000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-548000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-128000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-128000</v>
-      </c>
+        <v>25000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-34539000</v>
+        <v>-5345000</v>
       </c>
       <c r="AI5" t="n">
-        <v>103000</v>
+        <v>53000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-34642000</v>
+        <v>-5398000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1742340000</v>
+        <v>223814000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-159735000</v>
+        <v>780000</v>
       </c>
       <c r="AM5" t="n">
-        <v>9924000</v>
+        <v>87000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1622412000</v>
+        <v>246341000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2137536000</v>
+        <v>94483000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1153491000</v>
+        <v>356053000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1453808000</v>
+        <v>23681000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-214807000</v>
+        <v>-227876000</v>
       </c>
       <c r="AS5" t="n">
-        <v>130717000</v>
+        <v>247397000</v>
       </c>
       <c r="AT5" t="n">
-        <v>34945000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4303000</v>
-      </c>
+        <v>2392000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>30642000</v>
+        <v>2392000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-38669000</v>
+        <v>421960000</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>-1976000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1000</v>
+        <v>-29000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-399199000</v>
+        <v>-56004000</v>
       </c>
       <c r="BA5" t="n">
-        <v>308250000</v>
+        <v>-2320610000</v>
       </c>
     </row>
   </sheetData>
@@ -3790,64 +3790,64 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
       <c r="DM1" t="inlineStr">
         <is>
           <t>longName</t>
@@ -3855,122 +3855,122 @@
       </c>
       <c r="DN1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.443</v>
+        <v>0.469</v>
       </c>
       <c r="AF2" t="n">
         <v>17740</v>
@@ -4233,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>3.5</v>
@@ -4350,113 +4350,113 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>1743405227</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>finmb_10246206</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-2.7522924</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
           <t>GLORY SUN LAND</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>1743405227</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>finmb_10246206</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-2.7522924</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.106</v>
-      </c>
       <c r="DM2" t="inlineStr">
         <is>
           <t>Glory Sun Land Group Limited</t>
         </is>
       </c>
-      <c r="DN2" t="n">
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1148520600000</v>
+      </c>
+      <c r="DP2" t="n">
         <v>-0.0029999986</v>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>0.106 - 0.106</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
       <c r="DS2" t="n">
         <v>0</v>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>0.106 - 0.106</t>
         </is>
       </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>1756292340</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EA2" t="n">
         <v>1756728000</v>
       </c>
-      <c r="DZ2" t="b">
+      <c r="EB2" t="b">
         <v>1</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EC2" t="n">
         <v>-3.92</v>
       </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
       <c r="ED2" t="n">
         <v>0</v>
       </c>
@@ -4464,22 +4464,22 @@
         <v>0</v>
       </c>
       <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
         <v>-0.024356617</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1148520600000</v>
+      <c r="EK2" t="b">
+        <v>0</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
